--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486861_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486861_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2175</v>
+        <v>5.8219</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6298</v>
+        <v>7.2342</v>
       </c>
       <c r="F2" t="n">
         <v>-1.4123</v>
@@ -610,10 +610,10 @@
         <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0891</v>
+        <v>0.6935</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3916</v>
+        <v>0.2129</v>
       </c>
       <c r="U2" t="n">
         <v>0.4806</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0566</v>
+        <v>1.5895</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3771</v>
+        <v>3.1175</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3205</v>
+        <v>-1.528</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3343</v>
@@ -688,13 +688,13 @@
         <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4463</v>
+        <v>0.9792</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4957</v>
+        <v>0.2361</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9506</v>
+        <v>0.7431</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6982</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.0749</v>
+        <v>-0.6698</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6431</v>
+        <v>1.8407</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.718</v>
+        <v>-2.5105</v>
       </c>
       <c r="G4" t="n">
         <v>0.8182</v>
@@ -766,13 +766,13 @@
         <v>0.616</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7412</v>
+        <v>-0.3361</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3216</v>
+        <v>-0.124</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4196</v>
+        <v>-0.2121</v>
       </c>
       <c r="V4" t="n">
         <v>-1.7679</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2104</v>
+        <v>-0.7048</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2277</v>
+        <v>-0.0185</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9827</v>
+        <v>-0.6863</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4975</v>
@@ -844,13 +844,13 @@
         <v>0.8214</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7478</v>
+        <v>-0.2421</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3875</v>
+        <v>-0.1783</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3603</v>
+        <v>-0.0638</v>
       </c>
       <c r="V5" t="n">
         <v>0.2402</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4191</v>
+        <v>-1.5697</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5885</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1694</v>
+        <v>-0.6902</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5315</v>
@@ -922,13 +922,13 @@
         <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3527</v>
+        <v>1.2021</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.531</v>
+        <v>0.178</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8837</v>
+        <v>1.0241</v>
       </c>
       <c r="V6" t="n">
         <v>-1.4189</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. FERRER IGLESIA</t>
+          <t>F. GARRIDO TEBAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7837</v>
+        <v>-2.1695</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2509</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-2.7839</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5945</v>
+        <v>-1.118</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1102</v>
+        <v>-2.0311</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4843</v>
+        <v>0.9131</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4621</v>
+        <v>1.0647</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3042</v>
+        <v>-0.1718</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1579</v>
+        <v>1.2365</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8676</v>
+        <v>-2.1827</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.194</v>
+        <v>-1.8593</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3264</v>
+        <v>-0.3234</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.8748</v>
+        <v>0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1948</v>
+        <v>-0.2363</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0653</v>
+        <v>0.0076</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1295</v>
+        <v>-0.244</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6982</v>
+        <v>-1.6366</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6982</v>
+        <v>-0.4579</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. GARRIDO TEBAN</t>
+          <t>N. FERRER IGLESIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5524</v>
+        <v>-2.1881</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5873</v>
+        <v>-1.7739</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1396</v>
+        <v>-0.4142</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.118</v>
+        <v>0.5945</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0311</v>
+        <v>0.1102</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9131</v>
+        <v>0.4843</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0647</v>
+        <v>1.4621</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1718</v>
+        <v>1.3042</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2365</v>
+        <v>0.1579</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1827</v>
+        <v>-0.8676</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8593</v>
+        <v>-1.194</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3234</v>
+        <v>0.3264</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8214</v>
+        <v>-2.8748</v>
       </c>
       <c r="Q8" t="n">
+        <v>-3.0801</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.7904</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.6982</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.6982</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.8214</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.6192</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.0195</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.5997</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-1.6366</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.4579</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.1786</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.0383</v>
+        <v>-5.6472</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0638</v>
+        <v>-2.7616</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9745</v>
+        <v>-2.8856</v>
       </c>
       <c r="G9" t="n">
         <v>-7.674</v>
@@ -1156,13 +1156,13 @@
         <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2374</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0622</v>
+        <v>0.24</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2996</v>
+        <v>0.3885</v>
       </c>
       <c r="V9" t="n">
         <v>0.3716</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.3052</v>
+        <v>-6.5962</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8758</v>
+        <v>-4.1668</v>
       </c>
       <c r="F10" t="n">
         <v>-2.4294</v>
@@ -1234,10 +1234,10 @@
         <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.74</v>
+        <v>-0.031</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0308</v>
+        <v>-0.3217</v>
       </c>
       <c r="U10" t="n">
         <v>0.2907</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-14.1099</v>
+        <v>-12.1339</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2306</v>
+        <v>3.206500000000001</v>
       </c>
       <c r="F11" t="n">
         <v>-15.3404</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.195699999999999</v>
+        <v>-6.1957</v>
       </c>
       <c r="H11" t="n">
         <v>-0.2761</v>
@@ -1312,10 +1312,10 @@
         <v>9.240399999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4721</v>
+        <v>3.448199999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1832</v>
+        <v>0.7929</v>
       </c>
       <c r="U11" t="n">
         <v>2.6551</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.6262</v>
+        <v>6.3734</v>
       </c>
       <c r="E12" t="n">
-        <v>4.5504</v>
+        <v>4.0274</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0758</v>
+        <v>2.346</v>
       </c>
       <c r="G12" t="n">
         <v>4.0663</v>
@@ -1390,13 +1390,13 @@
         <v>1.6427</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9706</v>
+        <v>0.7178</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4144</v>
+        <v>-0.1087</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5562</v>
+        <v>0.8264</v>
       </c>
       <c r="V12" t="n">
         <v>1.1786</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7293</v>
+        <v>4.8068</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3018</v>
+        <v>3.4064</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4275</v>
+        <v>1.4004</v>
       </c>
       <c r="G13" t="n">
         <v>1.312</v>
@@ -1468,13 +1468,13 @@
         <v>2.2588</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5293</v>
+        <v>0.5482</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4147</v>
+        <v>-0.3101</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1145</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>2.9466</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4143</v>
+        <v>2.9495</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4121</v>
+        <v>1.9351</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0022</v>
+        <v>1.0144</v>
       </c>
       <c r="G14" t="n">
         <v>1.1779</v>
@@ -1546,13 +1546,13 @@
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0393</v>
+        <v>0.5744</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3174</v>
+        <v>-0.7944</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3567</v>
+        <v>1.3689</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2402</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9468</v>
+        <v>2.3773</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7637</v>
+        <v>4.1821</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8169</v>
+        <v>-1.8047</v>
       </c>
       <c r="G15" t="n">
         <v>1.3768</v>
@@ -1624,13 +1624,13 @@
         <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1942</v>
+        <v>0.6248</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7905</v>
+        <v>-0.3721</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9847</v>
+        <v>0.9968</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2402</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3615</v>
+        <v>0.5759</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3647</v>
+        <v>2.5642</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7262</v>
+        <v>-1.9883</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1689</v>
+        <v>-0.3175</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1626</v>
+        <v>-0.8728</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3314</v>
+        <v>0.5552</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0886</v>
+        <v>2.2651</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0492</v>
+        <v>0.3183</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0395</v>
+        <v>1.9469</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2575</v>
+        <v>-2.5827</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1134</v>
+        <v>-1.191</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3709</v>
+        <v>-1.3917</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.291</v>
+        <v>0.0988</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4534</v>
+        <v>-0.0931</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1624</v>
+        <v>0.1919</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2586</v>
+        <v>0.4365</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5642</v>
+        <v>-0.2601</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3056</v>
+        <v>0.6966</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3175</v>
+        <v>-0.1689</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8728</v>
+        <v>0.1626</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5552</v>
+        <v>-0.3314</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2651</v>
+        <v>0.0886</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3183</v>
+        <v>0.0492</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9469</v>
+        <v>0.0395</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5827</v>
+        <v>-0.2575</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.191</v>
+        <v>0.1134</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3917</v>
+        <v>-0.3709</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2185</v>
+        <v>-0.216</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0931</v>
+        <v>-0.3488</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1254</v>
+        <v>0.1328</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. HIERREZUELO SERER</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0051</v>
+        <v>0.1554</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.2564</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0819</v>
+        <v>0.4118</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3112</v>
+        <v>1.7013</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.3293</v>
+        <v>0.12</v>
       </c>
       <c r="I18" t="n">
-        <v>0.018</v>
+        <v>1.5813</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8781</v>
+        <v>1.2508</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2195</v>
+        <v>0.6458</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3414</v>
+        <v>0.605</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4332</v>
+        <v>0.4505</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1098</v>
+        <v>-0.5258</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3234</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
         <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4293</v>
+        <v>-0.7904</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6042</v>
+        <v>-0.4805</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1749</v>
+        <v>-0.3098</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8768</v>
+        <v>-0.9609</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.4579</v>
+        <v>-0.9609</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>J. HIERREZUELO SERER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6048</v>
+        <v>-0.2736</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.361</v>
+        <v>-0.7147</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2438</v>
+        <v>0.441</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7013</v>
+        <v>-2.3112</v>
       </c>
       <c r="H19" t="n">
-        <v>0.12</v>
+        <v>-2.3293</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5813</v>
+        <v>0.018</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2508</v>
+        <v>-0.8781</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6458</v>
+        <v>-1.2195</v>
       </c>
       <c r="L19" t="n">
-        <v>0.605</v>
+        <v>0.3414</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4505</v>
+        <v>-1.4332</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5258</v>
+        <v>-1.1098</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9762999999999999</v>
+        <v>-0.3234</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R19" t="n">
         <v>1.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5505</v>
+        <v>0.1608</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5851</v>
+        <v>-0.0234</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9654</v>
+        <v>0.1842</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9609</v>
+        <v>1.8768</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9609</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6168</v>
+        <v>-0.5017</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.4564</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1778</v>
+        <v>-0.9581</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6408</v>
@@ -2014,13 +2014,13 @@
         <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5161</v>
+        <v>-0.401</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0195</v>
+        <v>-0.1241</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4966</v>
+        <v>-0.2769</v>
       </c>
       <c r="V20" t="n">
         <v>1.1561</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>14.11</v>
+        <v>16.8995</v>
       </c>
       <c r="E21" t="n">
-        <v>15.3405</v>
+        <v>15.3404</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2305</v>
+        <v>1.5591</v>
       </c>
       <c r="G21" t="n">
         <v>6.1959</v>
@@ -2092,13 +2092,13 @@
         <v>12.3206</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.472</v>
+        <v>1.3174</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.6551</v>
+        <v>-2.6552</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1832</v>
+        <v>3.972699999999999</v>
       </c>
       <c r="V21" t="n">
         <v>6.306100000000001</v>
